--- a/cucumber-for-appian/src/test/resources/testdata/End2End/04_NovatedApp_End2End.xlsx
+++ b/cucumber-for-appian/src/test/resources/testdata/End2End/04_NovatedApp_End2End.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="51">
   <si>
     <t>TC ID</t>
   </si>
@@ -119,19 +119,19 @@
     <t>N/A</t>
   </si>
   <si>
-    <t>REQ-629</t>
-  </si>
-  <si>
-    <t>ORIX Ampol</t>
+    <t>REQ-643</t>
+  </si>
+  <si>
+    <t>ORIX Motorpass</t>
   </si>
   <si>
     <t>Delivery Address *</t>
   </si>
   <si>
-    <t>Request Submission Date: 22 Apr 2026 09:06 PM</t>
-  </si>
-  <si>
-    <t>Last Update Date: 22 Apr 2026 09:06 PM</t>
+    <t>Request Submission Date: 29 Apr 2026 03:56 AM</t>
+  </si>
+  <si>
+    <t>Last Update Date: 29 Apr 2026 03:56 AM</t>
   </si>
   <si>
     <t>Request Subtype: New Fuel Card</t>
@@ -171,6 +171,15 @@
   </si>
   <si>
     <t>${TC001.Request Subtype}</t>
+  </si>
+  <si>
+    <t>REQ-657</t>
+  </si>
+  <si>
+    <t>Request Submission Date: 05 May 2026 03:30 AM</t>
+  </si>
+  <si>
+    <t>Last Update Date: 05 May 2026 03:31 AM</t>
   </si>
 </sst>
 </file>
@@ -840,10 +849,10 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="180" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -858,7 +867,7 @@
     <cellStyle name="Note" xfId="8" builtinId="10"/>
     <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
     <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
     <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
     <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
     <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
@@ -1187,27 +1196,27 @@
   <dimension ref="A1:AA10"/>
   <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="8.55833333333333" customWidth="1"/>
-    <col min="2" max="2" width="20.7" customWidth="1"/>
-    <col min="3" max="4" width="24.3333333333333" customWidth="1"/>
-    <col min="5" max="5" width="27.3333333333333" customWidth="1"/>
-    <col min="6" max="6" width="16.775" customWidth="1"/>
-    <col min="7" max="7" width="15.3333333333333" customWidth="1"/>
-    <col min="8" max="8" width="21.775" customWidth="1"/>
-    <col min="9" max="9" width="18.6666666666667" customWidth="1"/>
-    <col min="10" max="10" width="23.775" customWidth="1"/>
-    <col min="11" max="11" width="17.225" customWidth="1"/>
-    <col min="12" max="12" width="19.8916666666667" customWidth="1"/>
-    <col min="13" max="13" width="20.6666666666667" customWidth="1"/>
-    <col min="14" max="14" width="17.5583333333333" customWidth="1"/>
-    <col min="15" max="15" width="14.6666666666667" customWidth="1"/>
-    <col min="16" max="16" width="19.3333333333333" customWidth="1"/>
-    <col min="17" max="17" width="18.4416666666667" customWidth="1"/>
-    <col min="18" max="22" width="19.1083333333333" customWidth="1"/>
-    <col min="23" max="23" width="20.7" customWidth="1"/>
-    <col min="24" max="24" width="24.6" customWidth="1"/>
-    <col min="25" max="25" width="29.8" customWidth="1"/>
-    <col min="26" max="27" width="24.5" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="8.55833333333333"/>
+    <col min="2" max="2" customWidth="true" width="20.7"/>
+    <col min="3" max="4" customWidth="true" width="24.3333333333333"/>
+    <col min="5" max="5" customWidth="true" width="27.3333333333333"/>
+    <col min="6" max="6" customWidth="true" width="16.775"/>
+    <col min="7" max="7" customWidth="true" width="15.3333333333333"/>
+    <col min="8" max="8" customWidth="true" width="21.775"/>
+    <col min="9" max="9" customWidth="true" width="18.6666666666667"/>
+    <col min="10" max="10" customWidth="true" width="23.775"/>
+    <col min="11" max="11" customWidth="true" width="17.225"/>
+    <col min="12" max="12" customWidth="true" width="19.8916666666667"/>
+    <col min="13" max="13" customWidth="true" width="20.6666666666667"/>
+    <col min="14" max="14" customWidth="true" width="17.5583333333333"/>
+    <col min="15" max="15" customWidth="true" width="14.6666666666667"/>
+    <col min="16" max="16" customWidth="true" width="19.3333333333333"/>
+    <col min="17" max="17" customWidth="true" width="18.4416666666667"/>
+    <col min="18" max="22" customWidth="true" width="19.1083333333333"/>
+    <col min="23" max="23" customWidth="true" width="20.7"/>
+    <col min="24" max="24" customWidth="true" width="24.6"/>
+    <col min="25" max="25" customWidth="true" width="29.8"/>
+    <col min="26" max="27" customWidth="true" width="24.5"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="27.6" spans="1:27">
@@ -1337,25 +1346,25 @@
       <c r="S2" s="4"/>
       <c r="T2" s="4"/>
       <c r="U2" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="V2" s="8" t="str">
+        <v>48</v>
+      </c>
+      <c r="V2" s="7" t="str">
         <f>TEXT(E2,"#,##0")&amp;" km"</f>
         <v>0 km</v>
       </c>
-      <c r="W2" s="8" t="s">
+      <c r="W2" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="X2" s="8" t="s">
+      <c r="X2" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="Y2" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="Z2" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="AA2" s="8" t="s">
+      <c r="Y2" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="Z2" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="AA2" s="7" t="s">
         <v>35</v>
       </c>
     </row>
@@ -1434,10 +1443,10 @@
         <v>47</v>
       </c>
     </row>
-    <row r="5" spans="5:5">
-      <c r="E5" s="7"/>
+    <row r="5" spans="1:27">
+      <c r="E5" s="8"/>
     </row>
-    <row r="10" spans="21:21">
+    <row r="10" spans="1:27">
       <c r="U10" s="9"/>
     </row>
   </sheetData>

--- a/cucumber-for-appian/src/test/resources/testdata/End2End/04_NovatedApp_End2End.xlsx
+++ b/cucumber-for-appian/src/test/resources/testdata/End2End/04_NovatedApp_End2End.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="73">
   <si>
     <t>TC ID</t>
   </si>
@@ -110,6 +110,45 @@
     <t>Request Subtype</t>
   </si>
   <si>
+    <t>Driver Salutation</t>
+  </si>
+  <si>
+    <t>Driver First Name</t>
+  </si>
+  <si>
+    <t>Driver Last Name</t>
+  </si>
+  <si>
+    <t>Driver Name</t>
+  </si>
+  <si>
+    <t>Driver Date of Birth</t>
+  </si>
+  <si>
+    <t>Driver Mobile Phone</t>
+  </si>
+  <si>
+    <t>Driver Email</t>
+  </si>
+  <si>
+    <t>Driver Your Residential Address</t>
+  </si>
+  <si>
+    <t>Driver Employer Name</t>
+  </si>
+  <si>
+    <t>Vehicle</t>
+  </si>
+  <si>
+    <t>Vehicle number</t>
+  </si>
+  <si>
+    <t>Vehicle name</t>
+  </si>
+  <si>
+    <t>Lease End Date</t>
+  </si>
+  <si>
     <t>TC001</t>
   </si>
   <si>
@@ -119,22 +158,28 @@
     <t>N/A</t>
   </si>
   <si>
-    <t>REQ-643</t>
+    <t>REQ-657</t>
   </si>
   <si>
     <t>ORIX Motorpass</t>
   </si>
   <si>
-    <t>Delivery Address *</t>
-  </si>
-  <si>
-    <t>Request Submission Date: 29 Apr 2026 03:56 AM</t>
-  </si>
-  <si>
-    <t>Last Update Date: 29 Apr 2026 03:56 AM</t>
-  </si>
-  <si>
-    <t>Request Subtype: New Fuel Card</t>
+    <t>05 May 2026 03:30 AM</t>
+  </si>
+  <si>
+    <t>05 May 2026 03:31 AM</t>
+  </si>
+  <si>
+    <t>New Fuel Card</t>
+  </si>
+  <si>
+    <t>VOLVO C40 - CPK418</t>
+  </si>
+  <si>
+    <t>CPK418</t>
+  </si>
+  <si>
+    <t>VOLVO C40</t>
   </si>
   <si>
     <t>TC002</t>
@@ -173,13 +218,34 @@
     <t>${TC001.Request Subtype}</t>
   </si>
   <si>
-    <t>REQ-657</t>
-  </si>
-  <si>
-    <t>Request Submission Date: 05 May 2026 03:30 AM</t>
-  </si>
-  <si>
-    <t>Last Update Date: 05 May 2026 03:31 AM</t>
+    <t>${TC001.Driver Salutation}</t>
+  </si>
+  <si>
+    <t>${TC001.Driver First Name}</t>
+  </si>
+  <si>
+    <t>${TC001.Driver Last Name}</t>
+  </si>
+  <si>
+    <t>${TC001.Driver Name}</t>
+  </si>
+  <si>
+    <t>${TC001.Driver Date of Birth}</t>
+  </si>
+  <si>
+    <t>${TC001.Driver Mobile Phone}</t>
+  </si>
+  <si>
+    <t>${TC001.Driver Email}</t>
+  </si>
+  <si>
+    <t>${TC001.Driver Your Residential Address}</t>
+  </si>
+  <si>
+    <t>${TC001.Driver Employer Name}</t>
+  </si>
+  <si>
+    <t>${TC001.Vehicle}</t>
   </si>
 </sst>
 </file>
@@ -1193,33 +1259,37 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AA10"/>
+  <dimension ref="A1:AN10"/>
   <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="8.55833333333333"/>
-    <col min="2" max="2" customWidth="true" width="20.7"/>
-    <col min="3" max="4" customWidth="true" width="24.3333333333333"/>
-    <col min="5" max="5" customWidth="true" width="27.3333333333333"/>
-    <col min="6" max="6" customWidth="true" width="16.775"/>
-    <col min="7" max="7" customWidth="true" width="15.3333333333333"/>
-    <col min="8" max="8" customWidth="true" width="21.775"/>
-    <col min="9" max="9" customWidth="true" width="18.6666666666667"/>
-    <col min="10" max="10" customWidth="true" width="23.775"/>
-    <col min="11" max="11" customWidth="true" width="17.225"/>
-    <col min="12" max="12" customWidth="true" width="19.8916666666667"/>
-    <col min="13" max="13" customWidth="true" width="20.6666666666667"/>
-    <col min="14" max="14" customWidth="true" width="17.5583333333333"/>
-    <col min="15" max="15" customWidth="true" width="14.6666666666667"/>
-    <col min="16" max="16" customWidth="true" width="19.3333333333333"/>
-    <col min="17" max="17" customWidth="true" width="18.4416666666667"/>
-    <col min="18" max="22" customWidth="true" width="19.1083333333333"/>
-    <col min="23" max="23" customWidth="true" width="20.7"/>
-    <col min="24" max="24" customWidth="true" width="24.6"/>
-    <col min="25" max="25" customWidth="true" width="29.8"/>
-    <col min="26" max="27" customWidth="true" width="24.5"/>
+    <col min="1" max="1" width="8.55833333333333" customWidth="1"/>
+    <col min="2" max="2" width="20.7" customWidth="1"/>
+    <col min="3" max="4" width="24.3333333333333" customWidth="1"/>
+    <col min="5" max="5" width="27.3333333333333" customWidth="1"/>
+    <col min="6" max="6" width="16.775" customWidth="1"/>
+    <col min="7" max="7" width="15.3333333333333" customWidth="1"/>
+    <col min="8" max="8" width="21.775" customWidth="1"/>
+    <col min="9" max="9" width="18.6666666666667" customWidth="1"/>
+    <col min="10" max="10" width="23.775" customWidth="1"/>
+    <col min="11" max="11" width="17.225" customWidth="1"/>
+    <col min="12" max="12" width="19.8916666666667" customWidth="1"/>
+    <col min="13" max="13" width="20.6666666666667" customWidth="1"/>
+    <col min="14" max="14" width="17.5583333333333" customWidth="1"/>
+    <col min="15" max="15" width="14.6666666666667" customWidth="1"/>
+    <col min="16" max="16" width="19.3333333333333" customWidth="1"/>
+    <col min="17" max="17" width="18.4416666666667" customWidth="1"/>
+    <col min="18" max="22" width="19.1083333333333" customWidth="1"/>
+    <col min="23" max="23" width="20.7" customWidth="1"/>
+    <col min="24" max="24" width="24.6" customWidth="1"/>
+    <col min="25" max="25" width="29.8" customWidth="1"/>
+    <col min="26" max="27" width="24.5" customWidth="1"/>
+    <col min="37" max="37" width="13.2" customWidth="1"/>
+    <col min="38" max="38" width="15.1" customWidth="1"/>
+    <col min="39" max="39" width="12.8" customWidth="1"/>
+    <col min="40" max="40" width="15.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="27.6" spans="1:27">
+    <row r="1" s="1" customFormat="1" ht="69" spans="1:40">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1301,13 +1371,52 @@
       <c r="AA1" s="3" t="s">
         <v>26</v>
       </c>
+      <c r="AB1" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF1" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG1" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH1" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AI1" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="AJ1" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="AK1" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL1" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="AM1" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="AN1" s="3" t="s">
+        <v>39</v>
+      </c>
     </row>
-    <row r="2" s="2" customFormat="1" ht="27.6" spans="1:27">
+    <row r="2" s="2" customFormat="1" ht="27.6" spans="1:40">
       <c r="A2" s="4" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="6"/>
@@ -1316,137 +1425,194 @@
       <c r="G2" s="4"/>
       <c r="H2" s="4"/>
       <c r="I2" s="4" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="N2" s="4" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="O2" s="4" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="P2" s="4" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="R2" s="4"/>
       <c r="S2" s="4"/>
       <c r="T2" s="4"/>
       <c r="U2" s="4" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="V2" s="7" t="str">
         <f>TEXT(E2,"#,##0")&amp;" km"</f>
         <v>0 km</v>
       </c>
       <c r="W2" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="X2" s="7" t="s">
-        <v>32</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="X2" s="7"/>
       <c r="Y2" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z2" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="AA2" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="AB2" s="7"/>
+      <c r="AC2" s="7"/>
+      <c r="AD2" s="7"/>
+      <c r="AE2" s="7" t="str">
+        <f>_xlfn.CONCAT(AC2," ",AD2)</f>
+        <v> </v>
+      </c>
+      <c r="AF2" s="7"/>
+      <c r="AG2" s="7"/>
+      <c r="AH2" s="7"/>
+      <c r="AI2" s="7"/>
+      <c r="AJ2" s="7"/>
+      <c r="AK2" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="AL2" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="Z2" s="7" t="s">
+      <c r="AM2" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="AA2" s="7" t="s">
-        <v>35</v>
-      </c>
+      <c r="AN2" s="7"/>
     </row>
-    <row r="3" s="2" customFormat="1" ht="27.6" spans="1:27">
+    <row r="3" s="2" customFormat="1" ht="82.8" spans="1:40">
       <c r="A3" s="4" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="D3" s="4"/>
       <c r="E3" s="4" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="F3" s="4"/>
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
       <c r="I3" s="4" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="M3" s="4" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="N3" s="4" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="O3" s="4" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="P3" s="4" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="R3" s="4" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="S3" s="4" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="U3" s="4" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="V3" s="4" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="W3" s="4" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="X3" s="4" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="Y3" s="4" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="Z3" s="4" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="AA3" s="4" t="s">
-        <v>47</v>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="AB3" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="AC3" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="AD3" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="AE3" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF3" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="AG3" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="AH3" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="AI3" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="AJ3" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="AK3" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="AL3" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="AM3" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="AN3" s="4"/>
     </row>
-    <row r="5" spans="1:27">
+    <row r="5" spans="1:40">
       <c r="E5" s="8"/>
     </row>
-    <row r="10" spans="1:27">
+    <row r="10" spans="1:40">
       <c r="U10" s="9"/>
     </row>
   </sheetData>

--- a/cucumber-for-appian/src/test/resources/testdata/End2End/04_NovatedApp_End2End.xlsx
+++ b/cucumber-for-appian/src/test/resources/testdata/End2End/04_NovatedApp_End2End.xlsx
@@ -9,7 +9,7 @@
   <sheets>
     <sheet name="TestData" sheetId="14" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="true"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="75">
   <si>
     <t>TC ID</t>
   </si>
@@ -158,28 +158,13 @@
     <t>N/A</t>
   </si>
   <si>
-    <t>REQ-657</t>
-  </si>
-  <si>
     <t>ORIX Motorpass</t>
   </si>
   <si>
-    <t>05 May 2026 03:30 AM</t>
-  </si>
-  <si>
-    <t>05 May 2026 03:31 AM</t>
-  </si>
-  <si>
     <t>New Fuel Card</t>
   </si>
   <si>
-    <t>VOLVO C40 - CPK418</t>
-  </si>
-  <si>
-    <t>CPK418</t>
-  </si>
-  <si>
-    <t>VOLVO C40</t>
+    <t>-</t>
   </si>
   <si>
     <t>TC002</t>
@@ -246,6 +231,27 @@
   </si>
   <si>
     <t>${TC001.Vehicle}</t>
+  </si>
+  <si>
+    <t>Mr</t>
+  </si>
+  <si>
+    <t>David</t>
+  </si>
+  <si>
+    <t>Stewart</t>
+  </si>
+  <si>
+    <t>30/10/1997</t>
+  </si>
+  <si>
+    <t>0499999999</t>
+  </si>
+  <si>
+    <t>visionpro101@gmail.com.test</t>
+  </si>
+  <si>
+    <t>Your Residential Address *</t>
   </si>
 </sst>
 </file>
@@ -1262,31 +1268,31 @@
   <dimension ref="A1:AN10"/>
   <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="8.55833333333333" customWidth="1"/>
-    <col min="2" max="2" width="20.7" customWidth="1"/>
-    <col min="3" max="4" width="24.3333333333333" customWidth="1"/>
-    <col min="5" max="5" width="27.3333333333333" customWidth="1"/>
-    <col min="6" max="6" width="16.775" customWidth="1"/>
-    <col min="7" max="7" width="15.3333333333333" customWidth="1"/>
-    <col min="8" max="8" width="21.775" customWidth="1"/>
-    <col min="9" max="9" width="18.6666666666667" customWidth="1"/>
-    <col min="10" max="10" width="23.775" customWidth="1"/>
-    <col min="11" max="11" width="17.225" customWidth="1"/>
-    <col min="12" max="12" width="19.8916666666667" customWidth="1"/>
-    <col min="13" max="13" width="20.6666666666667" customWidth="1"/>
-    <col min="14" max="14" width="17.5583333333333" customWidth="1"/>
-    <col min="15" max="15" width="14.6666666666667" customWidth="1"/>
-    <col min="16" max="16" width="19.3333333333333" customWidth="1"/>
-    <col min="17" max="17" width="18.4416666666667" customWidth="1"/>
-    <col min="18" max="22" width="19.1083333333333" customWidth="1"/>
-    <col min="23" max="23" width="20.7" customWidth="1"/>
-    <col min="24" max="24" width="24.6" customWidth="1"/>
-    <col min="25" max="25" width="29.8" customWidth="1"/>
-    <col min="26" max="27" width="24.5" customWidth="1"/>
-    <col min="37" max="37" width="13.2" customWidth="1"/>
-    <col min="38" max="38" width="15.1" customWidth="1"/>
-    <col min="39" max="39" width="12.8" customWidth="1"/>
-    <col min="40" max="40" width="15.5" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="8.55833333333333"/>
+    <col min="2" max="2" customWidth="true" width="20.7"/>
+    <col min="3" max="4" customWidth="true" width="24.3333333333333"/>
+    <col min="5" max="5" customWidth="true" width="27.3333333333333"/>
+    <col min="6" max="6" customWidth="true" width="16.775"/>
+    <col min="7" max="7" customWidth="true" width="15.3333333333333"/>
+    <col min="8" max="8" customWidth="true" width="21.775"/>
+    <col min="9" max="9" customWidth="true" width="18.6666666666667"/>
+    <col min="10" max="10" customWidth="true" width="23.775"/>
+    <col min="11" max="11" customWidth="true" width="17.225"/>
+    <col min="12" max="12" customWidth="true" width="19.8916666666667"/>
+    <col min="13" max="13" customWidth="true" width="20.6666666666667"/>
+    <col min="14" max="14" customWidth="true" width="17.5583333333333"/>
+    <col min="15" max="15" customWidth="true" width="14.6666666666667"/>
+    <col min="16" max="16" customWidth="true" width="19.3333333333333"/>
+    <col min="17" max="17" customWidth="true" width="18.4416666666667"/>
+    <col min="18" max="22" customWidth="true" width="19.1083333333333"/>
+    <col min="23" max="23" customWidth="true" width="20.7"/>
+    <col min="24" max="24" customWidth="true" width="24.6"/>
+    <col min="25" max="25" customWidth="true" width="29.8"/>
+    <col min="26" max="27" customWidth="true" width="24.5"/>
+    <col min="37" max="37" customWidth="true" width="13.2"/>
+    <col min="38" max="38" customWidth="true" width="15.1"/>
+    <col min="39" max="39" customWidth="true" width="12.8"/>
+    <col min="40" max="40" customWidth="true" width="15.5"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="69" spans="1:40">
@@ -1419,8 +1425,14 @@
         <v>41</v>
       </c>
       <c r="C2" s="5"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
+      <c r="D2" s="6" t="n">
+        <f>C2+1</f>
+        <v>1.0</v>
+      </c>
+      <c r="E2" s="6" t="n">
+        <f>D2</f>
+        <v>1.0</v>
+      </c>
       <c r="F2" s="4"/>
       <c r="G2" s="4"/>
       <c r="H2" s="4"/>
@@ -1454,62 +1466,69 @@
       <c r="R2" s="4"/>
       <c r="S2" s="4"/>
       <c r="T2" s="4"/>
-      <c r="U2" s="4" t="s">
-        <v>43</v>
-      </c>
+      <c r="U2" s="4"/>
       <c r="V2" s="7" t="str">
         <f>TEXT(E2,"#,##0")&amp;" km"</f>
-        <v>0 km</v>
+        <v>1 km</v>
       </c>
       <c r="W2" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="X2" s="7"/>
+      <c r="Y2" s="7"/>
+      <c r="Z2" s="7"/>
+      <c r="AA2" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="X2" s="7"/>
-      <c r="Y2" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="Z2" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="AA2" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="AB2" s="7"/>
-      <c r="AC2" s="7"/>
-      <c r="AD2" s="7"/>
+      <c r="AB2" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="AC2" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD2" s="7" t="s">
+        <v>70</v>
+      </c>
       <c r="AE2" s="7" t="str">
         <f>_xlfn.CONCAT(AC2," ",AD2)</f>
-        <v> </v>
-      </c>
-      <c r="AF2" s="7"/>
-      <c r="AG2" s="7"/>
-      <c r="AH2" s="7"/>
-      <c r="AI2" s="7"/>
-      <c r="AJ2" s="7"/>
-      <c r="AK2" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="AL2" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="AM2" s="7" t="s">
-        <v>50</v>
-      </c>
+        <v>David Stewart</v>
+      </c>
+      <c r="AF2" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="AG2" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="AH2" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="AI2" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="AJ2" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="AK2" s="7" t="str">
+        <f>AM2&amp;" - "&amp;AL2</f>
+        <v> - </v>
+      </c>
+      <c r="AL2" s="7"/>
+      <c r="AM2" s="7"/>
       <c r="AN2" s="7"/>
     </row>
     <row r="3" s="2" customFormat="1" ht="82.8" spans="1:40">
       <c r="A3" s="4" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>41</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="D3" s="4"/>
       <c r="E3" s="4" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="F3" s="4"/>
       <c r="G3" s="4"/>
@@ -1545,67 +1564,67 @@
         <v>42</v>
       </c>
       <c r="S3" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="T3" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="U3" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="V3" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="W3" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="X3" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="T3" s="4" t="s">
+      <c r="Y3" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="U3" s="4" t="s">
+      <c r="Z3" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="V3" s="4" t="s">
+      <c r="AA3" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="W3" s="4" t="s">
+      <c r="AB3" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="X3" s="4" t="s">
+      <c r="AC3" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="Y3" s="4" t="s">
+      <c r="AD3" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="Z3" s="4" t="s">
+      <c r="AE3" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="AA3" s="4" t="s">
+      <c r="AF3" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="AB3" s="4" t="s">
+      <c r="AG3" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="AC3" s="4" t="s">
+      <c r="AH3" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="AD3" s="4" t="s">
+      <c r="AI3" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="AE3" s="4" t="s">
+      <c r="AJ3" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="AF3" s="4" t="s">
+      <c r="AK3" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="AG3" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="AH3" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="AI3" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="AJ3" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="AK3" s="4" t="s">
-        <v>72</v>
-      </c>
       <c r="AL3" s="4" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="AM3" s="4" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="AN3" s="4"/>
     </row>

--- a/cucumber-for-appian/src/test/resources/testdata/End2End/04_NovatedApp_End2End.xlsx
+++ b/cucumber-for-appian/src/test/resources/testdata/End2End/04_NovatedApp_End2End.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="85">
   <si>
     <t>TC ID</t>
   </si>
@@ -155,16 +155,55 @@
     <t>Fuel Card</t>
   </si>
   <si>
+    <t>52339</t>
+  </si>
+  <si>
     <t>N/A</t>
   </si>
   <si>
+    <t>REQ-734</t>
+  </si>
+  <si>
     <t>ORIX Motorpass</t>
   </si>
   <si>
+    <t>Delivery Address *</t>
+  </si>
+  <si>
+    <t>19 May 2026 08:42 PM</t>
+  </si>
+  <si>
     <t>New Fuel Card</t>
   </si>
   <si>
-    <t>-</t>
+    <t>Mr</t>
+  </si>
+  <si>
+    <t>Neil</t>
+  </si>
+  <si>
+    <t>Jones</t>
+  </si>
+  <si>
+    <t>01/06/2000</t>
+  </si>
+  <si>
+    <t>0400123146</t>
+  </si>
+  <si>
+    <t>1 Sydney St, Mogo NSW 2536</t>
+  </si>
+  <si>
+    <t>Guild Insurance Ltd</t>
+  </si>
+  <si>
+    <t>YKQ26Y</t>
+  </si>
+  <si>
+    <t>MAZDA CX-5</t>
+  </si>
+  <si>
+    <t>25 Sept 2026</t>
   </si>
   <si>
     <t>TC002</t>
@@ -233,22 +272,13 @@
     <t>${TC001.Vehicle}</t>
   </si>
   <si>
-    <t>Mr</t>
-  </si>
-  <si>
-    <t>David</t>
-  </si>
-  <si>
-    <t>Stewart</t>
-  </si>
-  <si>
-    <t>30/10/1997</t>
-  </si>
-  <si>
-    <t>0499999999</t>
-  </si>
-  <si>
-    <t>visionpro101@gmail.com.test</t>
+    <t>${TC001.Vehicle number}</t>
+  </si>
+  <si>
+    <t>${TC001.Vehicle name}</t>
+  </si>
+  <si>
+    <t>neil.jones@exxonmobil.com.test</t>
   </si>
   <si>
     <t>Your Residential Address *</t>
@@ -1289,13 +1319,14 @@
     <col min="24" max="24" customWidth="true" width="24.6"/>
     <col min="25" max="25" customWidth="true" width="29.8"/>
     <col min="26" max="27" customWidth="true" width="24.5"/>
+    <col min="35" max="35" customWidth="true" width="21.6"/>
     <col min="37" max="37" customWidth="true" width="13.2"/>
     <col min="38" max="38" customWidth="true" width="15.1"/>
     <col min="39" max="39" customWidth="true" width="12.8"/>
     <col min="40" max="40" customWidth="true" width="15.5"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="69" spans="1:40">
+    <row r="1" s="1" customFormat="1" ht="41.4" spans="1:40">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1417,214 +1448,230 @@
         <v>39</v>
       </c>
     </row>
-    <row r="2" s="2" customFormat="1" ht="27.6" spans="1:40">
+    <row r="2" s="2" customFormat="1" ht="41.4" spans="1:40">
       <c r="A2" s="4" t="s">
         <v>40</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C2" s="5"/>
+      <c r="C2" s="5" t="s">
+        <v>42</v>
+      </c>
       <c r="D2" s="6" t="n">
         <f>C2+1</f>
-        <v>1.0</v>
+        <v>52340.0</v>
       </c>
       <c r="E2" s="6" t="n">
         <f>D2</f>
-        <v>1.0</v>
+        <v>52340.0</v>
       </c>
       <c r="F2" s="4"/>
       <c r="G2" s="4"/>
       <c r="H2" s="4"/>
       <c r="I2" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N2" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="O2" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P2" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="R2" s="4"/>
       <c r="S2" s="4"/>
       <c r="T2" s="4"/>
-      <c r="U2" s="4"/>
+      <c r="U2" s="4" t="s">
+        <v>44</v>
+      </c>
       <c r="V2" s="7" t="str">
         <f>TEXT(E2,"#,##0")&amp;" km"</f>
-        <v>1 km</v>
+        <v>52,340 km</v>
       </c>
       <c r="W2" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="X2" s="7"/>
-      <c r="Y2" s="7"/>
-      <c r="Z2" s="7"/>
+        <v>45</v>
+      </c>
+      <c r="X2" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y2" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z2" s="7" t="s">
+        <v>47</v>
+      </c>
       <c r="AA2" s="7" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AB2" s="7" t="s">
-        <v>68</v>
+        <v>49</v>
       </c>
       <c r="AC2" s="7" t="s">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="AD2" s="7" t="s">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="AE2" s="7" t="str">
         <f>_xlfn.CONCAT(AC2," ",AD2)</f>
-        <v>David Stewart</v>
+        <v>Neil Jones</v>
       </c>
       <c r="AF2" s="7" t="s">
-        <v>71</v>
+        <v>52</v>
       </c>
       <c r="AG2" s="7" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="AH2" s="7" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="AI2" s="7" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="AJ2" s="7" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="AK2" s="7" t="str">
         <f>AM2&amp;" - "&amp;AL2</f>
-        <v> - </v>
-      </c>
-      <c r="AL2" s="7"/>
-      <c r="AM2" s="7"/>
-      <c r="AN2" s="7"/>
+        <v>MAZDA CX-5 - YKQ26Y</v>
+      </c>
+      <c r="AL2" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="AM2" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="AN2" s="7" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="3" s="2" customFormat="1" ht="82.8" spans="1:40">
       <c r="A3" s="4" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>41</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="D3" s="4"/>
       <c r="E3" s="4" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="F3" s="4"/>
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
       <c r="I3" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M3" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N3" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="O3" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P3" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="R3" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="S3" s="4" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="U3" s="4" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="V3" s="4" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="W3" s="4" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="X3" s="4" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="Y3" s="4" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="Z3" s="4" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="AA3" s="4" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="AB3" s="4" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="AC3" s="4" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="AD3" s="4" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="AE3" s="4" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="AF3" s="4" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="AG3" s="4" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="AH3" s="4" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="AI3" s="4" t="s">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="AJ3" s="4" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="AK3" s="4" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="AL3" s="4" t="s">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="AM3" s="4" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="AN3" s="4"/>
     </row>
